--- a/survey_templates/039_islamic_finance_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/039_islamic_finance_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
